--- a/www/terminologies/CodeSystem-terminologie-cim-10.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-cim-10.xlsx
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>19161</t>
+    <t>19075</t>
   </si>
   <si>
     <t>Code</t>
